--- a/data/trans_orig/IP22_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28907</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>48045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81354</t>
+          <t>81221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93368</t>
+          <t>92910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68638</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81897</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153587</t>
+          <t>153853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>171118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29788</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14816</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34177</t>
+          <t>34883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52716</t>
+          <t>52682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70920</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>58002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71154</t>
+          <t>71233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>120677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139182</t>
+          <t>138476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31131</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48433</t>
+          <t>48435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>45606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56469</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68114</t>
+          <t>68487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82583</t>
+          <t>81960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118291</t>
+          <t>118289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>135368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>51771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35972</t>
+          <t>36139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>54939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73397</t>
+          <t>74453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99934</t>
+          <t>100056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148830</t>
+          <t>148962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167535</t>
+          <t>167399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146458</t>
+          <t>147135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166102</t>
+          <t>165935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302873</t>
+          <t>302751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>329410</t>
+          <t>328354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33373</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52653</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81741</t>
+          <t>82100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>94032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93824</t>
+          <t>93561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108378</t>
+          <t>107992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178757</t>
+          <t>179802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198037</t>
+          <t>198523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37401</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52456</t>
+          <t>52682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64430</t>
+          <t>64603</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53384</t>
+          <t>53683</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109861</t>
+          <t>110248</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125595</t>
+          <t>126430</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111208</t>
+          <t>111410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143092</t>
+          <t>146150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>134834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>168055</t>
+          <t>167885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>254998</t>
+          <t>256665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>303286</t>
+          <t>304374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>495764</t>
+          <t>492706</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>527648</t>
+          <t>527446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>516548</t>
+          <t>516718</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>551708</t>
+          <t>549769</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1020173</t>
+          <t>1019085</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1068461</t>
+          <t>1066794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28891</t>
+          <t>29027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>30019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35032</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61042</t>
+          <t>60906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74384</t>
+          <t>73662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60758</t>
+          <t>59744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>74040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126278</t>
+          <t>125635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144665</t>
+          <t>144957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>61331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62509</t>
+          <t>62640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76086</t>
+          <t>76314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61211</t>
+          <t>61270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>76096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127401</t>
+          <t>127971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147875</t>
+          <t>147992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28910</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46667</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62131</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74000</t>
+          <t>74487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60068</t>
+          <t>59072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72825</t>
+          <t>72665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126380</t>
+          <t>126452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144137</t>
+          <t>144043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>69389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56155</t>
+          <t>55591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78549</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111741</t>
+          <t>109967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142868</t>
+          <t>141466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137042</t>
+          <t>136719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158174</t>
+          <t>157832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148888</t>
+          <t>149641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171282</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290677</t>
+          <t>292079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321804</t>
+          <t>323578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>39702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52875</t>
+          <t>53500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61263</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87121</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109940</t>
+          <t>109467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126253</t>
+          <t>126020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>86670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106336</t>
+          <t>105137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202218</t>
+          <t>201939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228076</t>
+          <t>227576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41168</t>
+          <t>41227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>50314</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>50045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62052</t>
+          <t>62495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95389</t>
+          <t>94546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109904</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140641</t>
+          <t>140889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178897</t>
+          <t>177478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176958</t>
+          <t>176150</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216198</t>
+          <t>217400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>329834</t>
+          <t>329946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383899</t>
+          <t>383079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>499647</t>
+          <t>501066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>537903</t>
+          <t>537655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>498137</t>
+          <t>496935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>537377</t>
+          <t>538185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1008980</t>
+          <t>1009800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1063045</t>
+          <t>1062933</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27540</t>
+          <t>27205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44616</t>
+          <t>43915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72049</t>
+          <t>71606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>72462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86466</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137453</t>
+          <t>138154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154529</t>
+          <t>154864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>28452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45881</t>
+          <t>46331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80613</t>
+          <t>79228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92875</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>87892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100270</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172579</t>
+          <t>172129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190525</t>
+          <t>190008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>57140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55369</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65978</t>
+          <t>65869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107035</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120661</t>
+          <t>121164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67683</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93045</t>
+          <t>92618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170216</t>
+          <t>169711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189545</t>
+          <t>188392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165636</t>
+          <t>166530</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183382</t>
+          <t>184747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341386</t>
+          <t>341813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366748</t>
+          <t>368474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>41562</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>63162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102628</t>
+          <t>102672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117288</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108167</t>
+          <t>109686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>125114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216817</t>
+          <t>216120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237518</t>
+          <t>237720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49977</t>
+          <t>49626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>57859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62652</t>
+          <t>62698</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118792</t>
+          <t>118876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104381</t>
+          <t>103436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135328</t>
+          <t>134118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105612</t>
+          <t>104153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139176</t>
+          <t>139689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>219026</t>
+          <t>215393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>264577</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>537384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>567121</t>
+          <t>568066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569743</t>
+          <t>569230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603307</t>
+          <t>604766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1115844</t>
+          <t>1119231</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1161395</t>
+          <t>1165028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>28183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32934</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53201</t>
+          <t>52850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76328</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88961</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108807</t>
+          <t>108725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123122</t>
+          <t>123128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188169</t>
+          <t>188520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208436</t>
+          <t>209092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,47 +9031,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>25075</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>17510</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>34702</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>9,24%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>25075</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>17566</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>34463</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76922</t>
+          <t>77157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87210</t>
+          <t>87012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73440</t>
+          <t>74612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86738</t>
+          <t>86896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,47 +9144,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>164456</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>154829</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>172021</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>90,76%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>164456</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>155068</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>171965</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30379</t>
+          <t>31018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39011</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47455</t>
+          <t>48040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>84696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101469</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27439</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>162714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195318</t>
+          <t>193940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169729</t>
+          <t>169836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190833</t>
+          <t>190785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343189</t>
+          <t>341403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381224</t>
+          <t>380135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35770</t>
+          <t>34709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>32693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55514</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105633</t>
+          <t>106232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126847</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146351</t>
+          <t>146511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226531</t>
+          <t>225837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249313</t>
+          <t>249352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56754</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66257</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60359</t>
+          <t>60882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121645</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133975</t>
+          <t>133731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83342</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123822</t>
+          <t>125224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97066</t>
+          <t>96330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135642</t>
+          <t>134459</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190028</t>
+          <t>191366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247636</t>
+          <t>245157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>532792</t>
+          <t>531390</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>573272</t>
+          <t>571490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>613583</t>
+          <t>614766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>652159</t>
+          <t>652895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1158203</t>
+          <t>1160682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1215811</t>
+          <t>1214473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
